--- a/public/TEMPLATE MENU UPLOAD DATA SISWA.xlsx
+++ b/public/TEMPLATE MENU UPLOAD DATA SISWA.xlsx
@@ -1,29 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
-  <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\yogyakarta_mualimat_penerimaan\public\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA084614-A893-4D6F-8F9D-2159D5520D78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xml:space="preserve">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView activeTab="2" autoFilterDateGrouping="true" firstSheet="0" minimized="false" showHorizontalScroll="true" showSheetTabs="true" showVerticalScroll="true" tabRatio="760" visibility="visible"/>
   </bookViews>
   <sheets>
-    <sheet name="UPLOAD DATA SISWA (NIS saja)" sheetId="3" r:id="rId1"/>
-    <sheet name="UPLOAD DATA SISWA (NIS &amp; nodaf)" sheetId="1" r:id="rId2"/>
-    <sheet name="UPLOAD DATA SISWA (nodaf saja)" sheetId="4" r:id="rId3"/>
-    <sheet name="Keterangan" sheetId="2" r:id="rId4"/>
+    <sheet name="UPLOAD DATA SISWA (NIS saja)" sheetId="1" r:id="rId4"/>
+    <sheet name="UPLOAD DATA SISWA (NIS &amp; nodaf)" sheetId="2" r:id="rId5"/>
+    <sheet name="UPLOAD DATA SISWA (nodaf saja)" sheetId="3" r:id="rId6"/>
+    <sheet name="Keterangan" sheetId="4" r:id="rId7"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="63">
   <si>
     <t>NIS</t>
   </si>
@@ -49,69 +44,138 @@
     <t>ALAMAT</t>
   </si>
   <si>
+    <t>ORTU</t>
+  </si>
+  <si>
+    <t>Fulan 1</t>
+  </si>
+  <si>
+    <t>MTS</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>2026/2027</t>
+  </si>
+  <si>
     <t>L</t>
   </si>
   <si>
     <t>Semarang</t>
   </si>
   <si>
+    <t>Gatot</t>
+  </si>
+  <si>
+    <t>Fulan 2</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>P</t>
+  </si>
+  <si>
+    <t>Solo</t>
+  </si>
+  <si>
     <t>Sehun</t>
   </si>
   <si>
-    <t>P</t>
-  </si>
-  <si>
-    <t>Fulan 1</t>
-  </si>
-  <si>
-    <t>Fulan 2</t>
-  </si>
-  <si>
     <t>Fulan 3</t>
   </si>
   <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>Niko</t>
+  </si>
+  <si>
     <t>Fulan 4</t>
   </si>
   <si>
+    <t>MA</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>Wonogiri</t>
+  </si>
+  <si>
+    <t>Doni</t>
+  </si>
+  <si>
     <t>Fulan 5</t>
   </si>
   <si>
+    <t>ICT</t>
+  </si>
+  <si>
+    <t>TESTING</t>
+  </si>
+  <si>
+    <t>2025/2026</t>
+  </si>
+  <si>
+    <t>Hema</t>
+  </si>
+  <si>
     <t>Fulan 6</t>
   </si>
   <si>
-    <t>A</t>
-  </si>
-  <si>
-    <t>B</t>
-  </si>
-  <si>
-    <t>2026/2027</t>
-  </si>
-  <si>
-    <t>2025/2026</t>
-  </si>
-  <si>
-    <t>Solo</t>
-  </si>
-  <si>
-    <t>Wonogiri</t>
-  </si>
-  <si>
-    <t>Gatot</t>
-  </si>
-  <si>
-    <t>Niko</t>
-  </si>
-  <si>
-    <t>Doni</t>
-  </si>
-  <si>
-    <t>Hema</t>
+    <t>12</t>
   </si>
   <si>
     <t>Roni</t>
   </si>
   <si>
+    <t>NO_WA</t>
+  </si>
+  <si>
+    <t>081234567801</t>
+  </si>
+  <si>
+    <t>081234567802</t>
+  </si>
+  <si>
+    <t>081234567803</t>
+  </si>
+  <si>
+    <t>081234567804</t>
+  </si>
+  <si>
+    <t>081234567805</t>
+  </si>
+  <si>
+    <t>081234567806</t>
+  </si>
+  <si>
+    <t>NODAFTAR</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>BARU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NB : </t>
+  </si>
+  <si>
+    <t>Yang dibaca oleh sistem adalah sheet paling kiri</t>
+  </si>
+  <si>
+    <t>kalau hendak meng upload sheet tertentu ,, bisa di geser sheet dimaksud ke sebelah kiri setelah itu di save dulu baru di uploadkan</t>
+  </si>
+  <si>
     <t>Maksimal kolom NIS 10 digit angka</t>
   </si>
   <si>
@@ -130,96 +194,54 @@
     <t>dari kolo NIS sampai kolom Angkatan wajib di isi</t>
   </si>
   <si>
+    <t>sedangkan kolom Alamat dan Ortu (nama perwakilan wali santri) bersifat opsional boleh di isi boleh tidak</t>
+  </si>
+  <si>
     <t>kalau di isi lebih bagus untuk mempermudah dalam pengelompokan dan pencarian datanya</t>
   </si>
   <si>
-    <t xml:space="preserve">NB : </t>
-  </si>
-  <si>
-    <t>Yang dibaca oleh sistem adalah sheet paling kiri</t>
-  </si>
-  <si>
-    <t>kalau hendak meng upload sheet tertentu ,, bisa di geser sheet dimaksud ke sebelah kiri setelah itu di save dulu baru di uploadkan</t>
-  </si>
-  <si>
-    <t>NODAFTAR</t>
-  </si>
-  <si>
-    <t>ORTU</t>
-  </si>
-  <si>
-    <t>MTS</t>
-  </si>
-  <si>
-    <t>MA</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>BARU</t>
-  </si>
-  <si>
-    <t>sedangkan kolom Alamat dan Ortu (nama perwakilan wali santri) bersifat opsional boleh di isi boleh tidak</t>
-  </si>
-  <si>
-    <t>ICT</t>
-  </si>
-  <si>
-    <t>TESTING</t>
+    <t>Kolom NO_WA opsional (nomor WhatsApp wali/siswa)</t>
+  </si>
+  <si>
+    <t>Isi dengan angka, contoh 081234567890 — formatkan kolom sebagai Text supaya 0 di depan tidak hilang</t>
+  </si>
+  <si>
+    <t>Kalau NO_WA dikosongkan, nomor WA yang sudah ada di sistem tidak diubah</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xml:space="preserve">
+  <numFmts count="0"/>
+  <fonts count="3">
     <font>
+      <b val="0"/>
+      <i val="0"/>
+      <strike val="0"/>
+      <u val="none"/>
       <sz val="11"/>
-      <color indexed="64"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
     <font>
+      <b val="1"/>
+      <i val="0"/>
+      <strike val="0"/>
+      <u val="none"/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
+      <b val="0"/>
+      <i val="0"/>
+      <strike val="0"/>
+      <u val="none"/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color indexed="64"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color indexed="64"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -240,53 +262,42 @@
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </left>
       <right style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </right>
       <top style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </bottom>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+  <cellXfs count="10">
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="1" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="0"/>
+    <xf xfId="0" fontId="0" numFmtId="49" fillId="0" borderId="1" applyFont="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="0"/>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="1" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="0"/>
+    <xf xfId="0" fontId="0" numFmtId="49" fillId="0" borderId="1" applyFont="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="0"/>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
+    <xf xfId="0" fontId="0" numFmtId="49" fillId="0" borderId="0" applyFont="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="0"/>
   </cellXfs>
-  <cellStyles count="3">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="2" xr:uid="{3BA2FF3F-91C0-470A-B360-894637E634E2}"/>
-    <cellStyle name="Normal 3" xfId="1" xr:uid="{874ECCDF-C017-4604-98FF-2A2398E68F17}"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <tableStyles defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotTableStyle1"/>
 </styleSheet>
 </file>
 
@@ -333,7 +344,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -385,7 +396,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -446,162 +457,190 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="35000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="80000">
               <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="40000">
               <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
   <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C07DFD7-A58D-4253-97E0-76E101863EAE}">
-  <dimension ref="A1:I7"/>
-  <sheetFormatPr defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xml:space="preserve" mc:Ignorable="x14ac">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+  </sheetPr>
+  <dimension ref="A1:J7"/>
+  <sheetFormatPr customHeight="true" defaultRowHeight="14.25" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.88671875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.33203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.33203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11" customWidth="true" style="0"/>
+    <col min="2" max="2" width="9.33203125" customWidth="true" style="0"/>
+    <col min="3" max="3" width="17.88671875" customWidth="true" style="0"/>
+    <col min="4" max="4" width="6.33203125" customWidth="true" style="0"/>
+    <col min="5" max="5" width="11" customWidth="true" style="0"/>
+    <col min="6" max="6" width="11.33203125" customWidth="true" style="0"/>
+    <col min="7" max="7" width="8.33203125" customWidth="true" style="0"/>
+    <col min="8" max="8" width="9.6640625" customWidth="true" style="0"/>
+    <col min="9" max="9" width="7.33203125" customWidth="true" style="0"/>
+    <col min="10" max="10" width="15.282" bestFit="true" customWidth="true" style="0"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" customHeight="1" ht="14.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -627,207 +666,242 @@
         <v>7</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" customHeight="1" ht="14.4">
       <c r="A2" s="2">
         <v>1234567801</v>
       </c>
       <c r="B2" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="D2" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>18</v>
-      </c>
       <c r="F2" s="3" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+      <c r="J2" s="9" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" customHeight="1" ht="14.4">
       <c r="A3" s="2">
         <v>1234567802</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="G3" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J3" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="D3" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="I3" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="4" spans="1:10" customHeight="1" ht="14.4">
       <c r="A4" s="2">
         <v>1234567803</v>
       </c>
       <c r="B4" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G4" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C4" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G4" s="6" t="s">
-        <v>8</v>
-      </c>
       <c r="H4" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="I4" s="3" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="5" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="J4" s="9" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" customHeight="1" ht="14.4">
       <c r="A5" s="2">
         <v>1234567804</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="E5" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G5" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="F5" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>11</v>
-      </c>
       <c r="H5" s="2" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+        <v>30</v>
+      </c>
+      <c r="J5" s="9" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" customHeight="1" ht="14.4">
       <c r="A6" s="2">
         <v>1234567805</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>52</v>
+        <v>33</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+        <v>35</v>
+      </c>
+      <c r="J6" s="9" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" customHeight="1" ht="14.4">
       <c r="A7" s="2">
         <v>1234567806</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>28</v>
+        <v>38</v>
+      </c>
+      <c r="J7" s="9" t="s">
+        <v>45</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51181100000000002" footer="0.51181100000000002"/>
-  <pageSetup scale="90" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <printOptions gridLines="false" gridLinesSet="true"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811" footer="0.511811"/>
+  <pageSetup paperSize="1" orientation="portrait" scale="90" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
+  <headerFooter differentOddEven="false" differentFirst="false" scaleWithDoc="true" alignWithMargins="true">
+    <oddHeader/>
+    <oddFooter/>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+  <tableParts count="0"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J7"/>
-  <sheetFormatPr defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xml:space="preserve" mc:Ignorable="x14ac">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+  </sheetPr>
+  <dimension ref="A1:K7"/>
+  <sheetFormatPr customHeight="true" defaultRowHeight="14.25" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.88671875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.33203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.33203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="6.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11" customWidth="true" style="0"/>
+    <col min="2" max="2" width="9.33203125" customWidth="true" style="0"/>
+    <col min="3" max="3" width="11" customWidth="true" style="0"/>
+    <col min="4" max="4" width="17.88671875" customWidth="true" style="0"/>
+    <col min="5" max="5" width="6.33203125" customWidth="true" style="0"/>
+    <col min="6" max="6" width="11" customWidth="true" style="0"/>
+    <col min="7" max="7" width="11.33203125" customWidth="true" style="0"/>
+    <col min="8" max="8" width="8.33203125" customWidth="true" style="0"/>
+    <col min="9" max="9" width="9.6640625" customWidth="true" style="0"/>
+    <col min="10" max="10" width="6.5546875" customWidth="true" style="0"/>
+    <col min="11" max="11" width="15.282" bestFit="true" customWidth="true" style="0"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" customHeight="1" ht="14.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -835,7 +909,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -856,226 +930,261 @@
         <v>7</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" customHeight="1" ht="14.4">
       <c r="A2" s="2">
         <v>1234567801</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C2" s="2">
         <v>1234567801</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>41</v>
+        <v>10</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>43</v>
+        <v>11</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+      <c r="K2" s="9" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" customHeight="1" ht="14.4">
       <c r="A3" s="2">
         <v>1234567802</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C3" s="2">
         <v>1234567802</v>
       </c>
       <c r="D3" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="K3" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="E3" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="4" spans="1:11" customHeight="1" ht="14.4">
       <c r="A4" s="2">
         <v>1234567803</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="C4" s="2">
         <v>1234567803</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>41</v>
+        <v>10</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>45</v>
+        <v>23</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="J4" s="3" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="5" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="K4" s="9" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" customHeight="1" ht="14.4">
       <c r="A5" s="2">
         <v>1234567804</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="C5" s="2">
         <v>1234567804</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="F5" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H5" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="G5" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>11</v>
-      </c>
       <c r="I5" s="2" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
+        <v>30</v>
+      </c>
+      <c r="K5" s="9" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" customHeight="1" ht="14.4">
       <c r="A6" s="2">
         <v>1234567805</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C6" s="2">
         <v>1234567805</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="E6" s="7" t="s">
         <v>47</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
+        <v>35</v>
+      </c>
+      <c r="K6" s="9" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" customHeight="1" ht="14.4">
       <c r="A7" s="2">
         <v>1234567806</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="C7" s="2">
         <v>1234567806</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>28</v>
+        <v>38</v>
+      </c>
+      <c r="K7" s="9" t="s">
+        <v>45</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51181100000000002" footer="0.51181100000000002"/>
-  <pageSetup scale="90" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <printOptions gridLines="false" gridLinesSet="true"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811" footer="0.511811"/>
+  <pageSetup paperSize="1" orientation="portrait" scale="90" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
+  <headerFooter differentOddEven="false" differentFirst="false" scaleWithDoc="true" alignWithMargins="true">
+    <oddHeader/>
+    <oddFooter/>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+  <tableParts count="0"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59F0334D-BFBC-4261-A2C8-DF7F09422AEE}">
-  <dimension ref="A1:I7"/>
-  <sheetFormatPr defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xml:space="preserve" mc:Ignorable="x14ac">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+  </sheetPr>
+  <dimension ref="A1:J7"/>
+  <sheetFormatPr customHeight="true" defaultRowHeight="14.25" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.88671875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.33203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.33203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="6.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11" customWidth="true" style="0"/>
+    <col min="2" max="2" width="9.33203125" customWidth="true" style="0"/>
+    <col min="3" max="3" width="17.88671875" customWidth="true" style="0"/>
+    <col min="4" max="4" width="6.33203125" customWidth="true" style="0"/>
+    <col min="5" max="5" width="11" customWidth="true" style="0"/>
+    <col min="6" max="6" width="11.33203125" customWidth="true" style="0"/>
+    <col min="7" max="7" width="8.33203125" customWidth="true" style="0"/>
+    <col min="8" max="8" width="9.6640625" customWidth="true" style="0"/>
+    <col min="9" max="9" width="6.5546875" customWidth="true" style="0"/>
+    <col min="10" max="10" width="15.282" bestFit="true" customWidth="true" style="0"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" customHeight="1" ht="14.4">
       <c r="A1" s="1" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -1099,250 +1208,310 @@
         <v>7</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" customHeight="1" ht="14.4">
       <c r="A2" s="2">
         <v>1234567801</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>41</v>
+        <v>10</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>43</v>
+        <v>11</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+      <c r="J2" s="9" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" customHeight="1" ht="14.4">
       <c r="A3" s="2">
         <v>1234567802</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="F3" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="G3" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J3" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="D3" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="I3" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="4" spans="1:10" customHeight="1" ht="14.4">
       <c r="A4" s="2">
         <v>1234567803</v>
       </c>
       <c r="B4" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G4" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C4" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="E4" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G4" s="6" t="s">
-        <v>8</v>
-      </c>
       <c r="H4" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="I4" s="3" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="5" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="J4" s="9" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" customHeight="1" ht="14.4">
       <c r="A5" s="2">
         <v>1234567804</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+        <v>30</v>
+      </c>
+      <c r="J5" s="9" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" customHeight="1" ht="14.4">
       <c r="A6" s="2">
         <v>1234567805</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+        <v>35</v>
+      </c>
+      <c r="J6" s="9" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" customHeight="1" ht="14.4">
       <c r="A7" s="2">
         <v>1234567806</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>28</v>
+        <v>38</v>
+      </c>
+      <c r="J7" s="9" t="s">
+        <v>45</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51181100000000002" footer="0.51181100000000002"/>
-  <pageSetup scale="90" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <printOptions gridLines="false" gridLinesSet="true"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811" footer="0.511811"/>
+  <pageSetup paperSize="1" orientation="portrait" scale="90" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
+  <headerFooter differentOddEven="false" differentFirst="false" scaleWithDoc="true" alignWithMargins="true">
+    <oddHeader/>
+    <oddFooter/>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+  <tableParts count="0"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8ACD2702-5769-414D-8DDB-A0ADB41CA288}">
-  <dimension ref="A1:A13"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xml:space="preserve" mc:Ignorable="x14ac">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+  </sheetPr>
+  <dimension ref="A1:A17"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1">
       <c r="A1" s="5" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1">
       <c r="A2" s="5" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
       <c r="A3" s="5" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
       <c r="A5" s="4" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
       <c r="A6" s="4" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
       <c r="A7" s="4" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
       <c r="A8" s="4" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
       <c r="A9" s="4" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
       <c r="A11" s="4" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
       <c r="A12" s="8" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
       <c r="A13" s="4" t="s">
-        <v>35</v>
+        <v>59</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1">
+      <c r="A16" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" t="s">
+        <v>62</v>
       </c>
     </row>
   </sheetData>
+  <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
+  <headerFooter differentOddEven="false" differentFirst="false" scaleWithDoc="true" alignWithMargins="true">
+    <oddHeader/>
+    <oddFooter/>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+  <tableParts count="0"/>
 </worksheet>
 </file>
--- a/public/TEMPLATE MENU UPLOAD DATA SISWA.xlsx
+++ b/public/TEMPLATE MENU UPLOAD DATA SISWA.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView activeTab="2" autoFilterDateGrouping="true" firstSheet="0" minimized="false" showHorizontalScroll="true" showSheetTabs="true" showVerticalScroll="true" tabRatio="760" visibility="visible"/>
+    <workbookView activeTab="0" autoFilterDateGrouping="true" firstSheet="0" minimized="false" showHorizontalScroll="true" showSheetTabs="true" showVerticalScroll="true" tabRatio="760" visibility="visible"/>
   </bookViews>
   <sheets>
     <sheet name="UPLOAD DATA SISWA (NIS saja)" sheetId="1" r:id="rId4"/>
@@ -47,6 +47,9 @@
     <t>ORTU</t>
   </si>
   <si>
+    <t>NO_WA</t>
+  </si>
+  <si>
     <t>Fulan 1</t>
   </si>
   <si>
@@ -71,6 +74,9 @@
     <t>Gatot</t>
   </si>
   <si>
+    <t>081234567801</t>
+  </si>
+  <si>
     <t>Fulan 2</t>
   </si>
   <si>
@@ -86,6 +92,9 @@
     <t>Sehun</t>
   </si>
   <si>
+    <t>081234567802</t>
+  </si>
+  <si>
     <t>Fulan 3</t>
   </si>
   <si>
@@ -98,6 +107,9 @@
     <t>Niko</t>
   </si>
   <si>
+    <t>081234567803</t>
+  </si>
+  <si>
     <t>Fulan 4</t>
   </si>
   <si>
@@ -113,6 +125,9 @@
     <t>Doni</t>
   </si>
   <si>
+    <t>081234567804</t>
+  </si>
+  <si>
     <t>Fulan 5</t>
   </si>
   <si>
@@ -128,6 +143,9 @@
     <t>Hema</t>
   </si>
   <si>
+    <t>081234567805</t>
+  </si>
+  <si>
     <t>Fulan 6</t>
   </si>
   <si>
@@ -135,24 +153,6 @@
   </si>
   <si>
     <t>Roni</t>
-  </si>
-  <si>
-    <t>NO_WA</t>
-  </si>
-  <si>
-    <t>081234567801</t>
-  </si>
-  <si>
-    <t>081234567802</t>
-  </si>
-  <si>
-    <t>081234567803</t>
-  </si>
-  <si>
-    <t>081234567804</t>
-  </si>
-  <si>
-    <t>081234567805</t>
   </si>
   <si>
     <t>081234567806</t>
@@ -637,7 +637,7 @@
     <col min="7" max="7" width="8.33203125" customWidth="true" style="0"/>
     <col min="8" max="8" width="9.6640625" customWidth="true" style="0"/>
     <col min="9" max="9" width="7.33203125" customWidth="true" style="0"/>
-    <col min="10" max="10" width="15.282" bestFit="true" customWidth="true" style="0"/>
+    <col min="10" max="10" width="15.282" customWidth="true" style="0"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" customHeight="1" ht="14.4">
@@ -669,7 +669,7 @@
         <v>8</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>39</v>
+        <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:10" customHeight="1" ht="14.4">
@@ -677,31 +677,31 @@
         <v>1234567801</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:10" customHeight="1" ht="14.4">
@@ -709,31 +709,31 @@
         <v>1234567802</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J3" s="9" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:10" customHeight="1" ht="14.4">
@@ -741,31 +741,31 @@
         <v>1234567803</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="J4" s="9" t="s">
-        <v>42</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5" spans="1:10" customHeight="1" ht="14.4">
@@ -773,31 +773,31 @@
         <v>1234567804</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C5" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="D5" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>24</v>
-      </c>
       <c r="F5" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="J5" s="9" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
     </row>
     <row r="6" spans="1:10" customHeight="1" ht="14.4">
@@ -805,31 +805,31 @@
         <v>1234567805</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C6" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C6" s="6" t="s">
-        <v>27</v>
-      </c>
       <c r="D6" s="7" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="J6" s="9" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="7" spans="1:10" customHeight="1" ht="14.4">
@@ -837,28 +837,28 @@
         <v>1234567806</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="J7" s="9" t="s">
         <v>45</v>
@@ -898,7 +898,7 @@
     <col min="8" max="8" width="8.33203125" customWidth="true" style="0"/>
     <col min="9" max="9" width="9.6640625" customWidth="true" style="0"/>
     <col min="10" max="10" width="6.5546875" customWidth="true" style="0"/>
-    <col min="11" max="11" width="15.282" bestFit="true" customWidth="true" style="0"/>
+    <col min="11" max="11" width="15.282" customWidth="true" style="0"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" customHeight="1" ht="14.4">
@@ -933,7 +933,7 @@
         <v>8</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>39</v>
+        <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:11" customHeight="1" ht="14.4">
@@ -941,34 +941,34 @@
         <v>1234567801</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C2" s="2">
         <v>1234567801</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K2" s="9" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:11" customHeight="1" ht="14.4">
@@ -976,34 +976,34 @@
         <v>1234567802</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C3" s="2">
         <v>1234567802</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="K3" s="9" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:11" customHeight="1" ht="14.4">
@@ -1011,34 +1011,34 @@
         <v>1234567803</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C4" s="2">
         <v>1234567803</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="K4" s="9" t="s">
-        <v>42</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5" spans="1:11" customHeight="1" ht="14.4">
@@ -1046,34 +1046,34 @@
         <v>1234567804</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C5" s="2">
         <v>1234567804</v>
       </c>
       <c r="D5" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="E5" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>24</v>
-      </c>
       <c r="G5" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="K5" s="9" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
     </row>
     <row r="6" spans="1:11" customHeight="1" ht="14.4">
@@ -1081,34 +1081,34 @@
         <v>1234567805</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="C6" s="2">
         <v>1234567805</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="E6" s="7" t="s">
         <v>47</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="K6" s="9" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="7" spans="1:11" customHeight="1" ht="14.4">
@@ -1116,31 +1116,31 @@
         <v>1234567806</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="C7" s="2">
         <v>1234567806</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="K7" s="9" t="s">
         <v>45</v>
@@ -1179,7 +1179,7 @@
     <col min="7" max="7" width="8.33203125" customWidth="true" style="0"/>
     <col min="8" max="8" width="9.6640625" customWidth="true" style="0"/>
     <col min="9" max="9" width="6.5546875" customWidth="true" style="0"/>
-    <col min="10" max="10" width="15.282" bestFit="true" customWidth="true" style="0"/>
+    <col min="10" max="10" width="15.282" customWidth="true" style="0"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" customHeight="1" ht="14.4">
@@ -1211,7 +1211,7 @@
         <v>8</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>39</v>
+        <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:10" customHeight="1" ht="14.4">
@@ -1219,31 +1219,31 @@
         <v>1234567801</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E2" s="6" t="s">
         <v>48</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:10" customHeight="1" ht="14.4">
@@ -1251,31 +1251,31 @@
         <v>1234567802</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E3" s="6" t="s">
         <v>48</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J3" s="9" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:10" customHeight="1" ht="14.4">
@@ -1283,31 +1283,31 @@
         <v>1234567803</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>48</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="J4" s="9" t="s">
-        <v>42</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5" spans="1:10" customHeight="1" ht="14.4">
@@ -1315,31 +1315,31 @@
         <v>1234567804</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="E5" s="6" t="s">
         <v>48</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="J5" s="9" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
     </row>
     <row r="6" spans="1:10" customHeight="1" ht="14.4">
@@ -1347,31 +1347,31 @@
         <v>1234567805</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C6" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C6" s="6" t="s">
-        <v>27</v>
-      </c>
       <c r="D6" s="7" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>48</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="J6" s="9" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="7" spans="1:10" customHeight="1" ht="14.4">
@@ -1379,28 +1379,28 @@
         <v>1234567806</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="E7" s="6" t="s">
         <v>48</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="J7" s="9" t="s">
         <v>45</v>
